--- a/public/file/Telenor Bulk Return.xlsx
+++ b/public/file/Telenor Bulk Return.xlsx
@@ -29,7 +29,7 @@
     <t>Tracking Number</t>
   </si>
   <si>
-    <t>Returned By</t>
+    <t>Received/Refused By</t>
   </si>
 </sst>
 </file>
